--- a/data/trans_dic/Q45B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,33</t>
+          <t>0,26; 1,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,77</t>
+          <t>1,08; 2,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,08</t>
+          <t>0,51; 1,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,28</t>
+          <t>1,62; 3,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,5</t>
+          <t>1,82; 3,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,33</t>
+          <t>0,22; 1,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,15</t>
+          <t>1,12; 2,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,93</t>
+          <t>1,65; 2,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,34</t>
+          <t>0,46; 1,32</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,15</t>
+          <t>1,62; 3,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,43</t>
+          <t>1,9; 3,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,26</t>
+          <t>0,46; 1,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 12,35</t>
+          <t>9,13; 12,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 10,33</t>
+          <t>7,58; 10,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,33</t>
+          <t>3,54; 5,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,21</t>
+          <t>5,53; 7,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 6,43</t>
+          <t>4,86; 6,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,0</t>
+          <t>2,08; 3,1</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,94</t>
+          <t>2,29; 5,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,95</t>
+          <t>2,0; 6,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,61</t>
+          <t>0,68; 2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 16,73</t>
+          <t>10,31; 16,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 19,81</t>
+          <t>12,29; 19,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,13</t>
+          <t>4,04; 8,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,15</t>
+          <t>6,53; 10,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,19</t>
+          <t>7,9; 11,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,79</t>
+          <t>2,59; 4,84</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,53</t>
+          <t>1,52; 2,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,11</t>
+          <t>1,93; 3,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,34</t>
+          <t>0,66; 1,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 8,74</t>
+          <t>6,95; 8,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,37</t>
+          <t>6,5; 8,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,11</t>
+          <t>2,9; 4,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,53</t>
+          <t>4,44; 5,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 5,57</t>
+          <t>4,56; 5,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 2,58</t>
+          <t>1,92; 2,63</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2895; 13678</t>
+          <t>2729; 12900</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9984; 26874</t>
+          <t>10515; 26361</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3843; 15625</t>
+          <t>3837; 14915</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20946; 43173</t>
+          <t>21325; 43568</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23194; 46647</t>
+          <t>24253; 47627</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2203; 13191</t>
+          <t>2199; 13277</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26729; 50538</t>
+          <t>26360; 50200</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37276; 67559</t>
+          <t>37948; 65062</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7889; 23376</t>
+          <t>7968; 22944</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27948; 53376</t>
+          <t>27513; 51083</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37690; 67186</t>
+          <t>37105; 67493</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9122; 26058</t>
+          <t>9529; 26023</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>149085; 196155</t>
+          <t>145027; 195151</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>133674; 180766</t>
+          <t>132730; 181414</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68807; 105469</t>
+          <t>69998; 106503</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>181306; 236428</t>
+          <t>181575; 236898</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>181039; 238504</t>
+          <t>180113; 238614</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83261; 121352</t>
+          <t>83992; 125397</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12632; 32740</t>
+          <t>12621; 32645</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9797; 28511</t>
+          <t>9583; 28816</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3695; 14224</t>
+          <t>3725; 14737</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48822; 79712</t>
+          <t>49134; 78081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58122; 90453</t>
+          <t>56108; 90187</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22362; 44661</t>
+          <t>22161; 44701</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67362; 104371</t>
+          <t>67163; 104117</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74248; 114071</t>
+          <t>73925; 111417</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28924; 52403</t>
+          <t>28350; 53040</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49328; 82988</t>
+          <t>49932; 83563</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68733; 106052</t>
+          <t>65791; 106102</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21863; 45075</t>
+          <t>22324; 45232</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>233817; 295437</t>
+          <t>234755; 298441</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>229681; 296346</t>
+          <t>230148; 296321</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>102245; 144785</t>
+          <t>101946; 145525</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>292503; 368021</t>
+          <t>295689; 368387</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>310144; 386748</t>
+          <t>316495; 390049</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>128610; 177568</t>
+          <t>131918; 181060</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q45B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,25</t>
+          <t>0,28; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,71</t>
+          <t>1,05; 2,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,99</t>
+          <t>0,52; 2,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,31</t>
+          <t>1,59; 3,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,57</t>
+          <t>1,77; 3,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,34</t>
+          <t>0,24; 1,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,14</t>
+          <t>1,12; 2,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,82</t>
+          <t>1,66; 2,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,32</t>
+          <t>0,45; 1,29</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,02</t>
+          <t>1,65; 3,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,45</t>
+          <t>1,9; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,26</t>
+          <t>0,45; 1,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 12,29</t>
+          <t>9,23; 12,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 10,36</t>
+          <t>7,63; 10,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,38</t>
+          <t>3,46; 5,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,22</t>
+          <t>5,52; 7,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,44</t>
+          <t>4,82; 6,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,1</t>
+          <t>2,02; 3,05</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,92</t>
+          <t>2,23; 5,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,02</t>
+          <t>2,15; 6,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,7</t>
+          <t>0,68; 2,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 16,39</t>
+          <t>10,36; 16,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,29; 19,75</t>
+          <t>12,84; 19,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,14</t>
+          <t>4,2; 8,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,13</t>
+          <t>6,66; 10,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,91</t>
+          <t>7,7; 11,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,84</t>
+          <t>2,63; 4,77</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,55</t>
+          <t>1,52; 2,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,11</t>
+          <t>1,99; 3,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,34</t>
+          <t>0,66; 1,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,83</t>
+          <t>6,94; 8,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 8,37</t>
+          <t>6,5; 8,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,13</t>
+          <t>2,94; 4,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,53</t>
+          <t>4,39; 5,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,61</t>
+          <t>4,52; 5,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,63</t>
+          <t>1,92; 2,6</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2729; 12900</t>
+          <t>2844; 14004</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10515; 26361</t>
+          <t>10192; 26282</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3837; 14915</t>
+          <t>3867; 15620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21325; 43568</t>
+          <t>20925; 43752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24253; 47627</t>
+          <t>23574; 48645</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2199; 13277</t>
+          <t>2385; 12619</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26360; 50200</t>
+          <t>26250; 51608</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37948; 65062</t>
+          <t>38280; 65388</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7968; 22944</t>
+          <t>7882; 22436</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27513; 51083</t>
+          <t>27863; 52485</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37105; 67493</t>
+          <t>37197; 65943</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9529; 26023</t>
+          <t>9308; 26359</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>145027; 195151</t>
+          <t>146487; 195181</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>132730; 181414</t>
+          <t>133620; 181220</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69998; 106503</t>
+          <t>68493; 104224</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>181575; 236898</t>
+          <t>181025; 237105</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>180113; 238614</t>
+          <t>178573; 237996</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83992; 125397</t>
+          <t>81749; 123554</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12621; 32645</t>
+          <t>12303; 32631</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9583; 28816</t>
+          <t>10309; 29988</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3725; 14737</t>
+          <t>3710; 14204</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49134; 78081</t>
+          <t>49334; 79494</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56108; 90187</t>
+          <t>58628; 90964</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22161; 44701</t>
+          <t>23041; 45703</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67163; 104117</t>
+          <t>68436; 105656</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>73925; 111417</t>
+          <t>72054; 111728</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28350; 53040</t>
+          <t>28801; 52254</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49932; 83563</t>
+          <t>49774; 82123</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65791; 106102</t>
+          <t>67906; 104363</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22324; 45232</t>
+          <t>22201; 44221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>234755; 298441</t>
+          <t>234665; 299743</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>230148; 296321</t>
+          <t>230229; 298667</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>101946; 145525</t>
+          <t>103504; 146177</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>295689; 368387</t>
+          <t>291859; 361735</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>316495; 390049</t>
+          <t>313959; 387725</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131918; 181060</t>
+          <t>132151; 178973</t>
         </is>
       </c>
     </row>
